--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Test ID</t>
   </si>
@@ -23,13 +23,25 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>All Modules</t>
+  </si>
+  <si>
+    <t>No cases for this filter</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -37,13 +49,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0F172A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,8 +79,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,24 +421,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="25" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -63,7 +63,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0F172A"/>
+        <fgColor rgb="15803D"/>
       </patternFill>
     </fill>
   </fills>
